--- a/i_test/test_D3_coorte_con_caratterizzazione/met.xlsx
+++ b/i_test/test_D3_coorte_con_caratterizzazione/met.xlsx
@@ -22,10 +22,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="5">
   <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">datasped</t>
+    <t xml:space="preserve">ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATE</t>
   </si>
   <si>
     <t xml:space="preserve">P01</t>
@@ -233,10 +233,10 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="2" t="n">
         <v>99</v>
       </c>
     </row>
@@ -249,10 +249,10 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="2" t="n">
         <v>101</v>
       </c>
     </row>
